--- a/Banking_VLOOKUP_Complete_Example.xlsx
+++ b/Banking_VLOOKUP_Complete_Example.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\salvataggi\SALVATAGGIO DATI\Documents\Seminari\Data Science (corsi)\Corso Data Science con Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE95330-ED17-419F-AB30-DF749CB0C0C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FBFC83-6900-46F7-A644-E74FE1D43E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VLOOKUP Example" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,14 +33,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
   <si>
     <t>VLOOKUP in Banking — Enriching Transactions with Product Information</t>
   </si>
   <si>
-    <t>Business scenario: the transaction table contains only an Account Code and a Transaction Amount. The Product Master table stores the business attributes associated with each Account Code. VLOOKUP uses the Account Code as a key to retrieve Product Name, Risk Category, and Annual Fee.</t>
-  </si>
-  <si>
     <t>Account Code</t>
   </si>
   <si>
@@ -96,6 +93,12 @@
   </si>
   <si>
     <t>Formula pattern: =VLOOKUP(lookup_value, table_array, column_index, FALSE)   Example: =VLOOKUP(A15,$E$7:$H$11,2,FALSE)</t>
+  </si>
+  <si>
+    <t>Business scenario: the transaction table contains only an Account Code and a Transaction Amount. The Product Master table stores the business attributes associated with each Account Code. VLOOKUP uses the Account Code as a key to retrieve Product Name, Risk Category, and Annual Fee, and this way enrich the final view</t>
+  </si>
+  <si>
+    <t>The original transaction table ENRICHED with product table data - JUST for VIEW (no storing)</t>
   </si>
 </sst>
 </file>
@@ -201,7 +204,62 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF4472C4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF70AD47"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -212,6 +270,30 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AAABB798-186A-44C8-80A5-A29C15643696}" name="Table1" displayName="Table1" ref="E6:H11" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="E6:H11" xr:uid="{AAABB798-186A-44C8-80A5-A29C15643696}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{DD56D30D-B4DE-4EFB-A878-C376FFC1E54C}" name="Account Code"/>
+    <tableColumn id="2" xr3:uid="{078DDD5C-99B5-41DD-9BA0-4E6B25C035F5}" name="Product Name"/>
+    <tableColumn id="3" xr3:uid="{CC09B622-D1B5-41CE-A630-F48FB194DA43}" name="Risk Category"/>
+    <tableColumn id="4" xr3:uid="{7CED65B8-F265-47C9-8AC1-6DEE2AD7EC1E}" name="Annual Fee (EUR)" dataDxfId="3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7F17D5E1-7BC4-42E4-BF75-F93636F10E6F}" name="Table2" displayName="Table2" ref="A6:B11" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A6:B11" xr:uid="{7F17D5E1-7BC4-42E4-BF75-F93636F10E6F}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{2F81024F-0A5C-4B0C-A722-37FE1F5D4C9A}" name="Account Code"/>
+    <tableColumn id="2" xr3:uid="{2E6CC9D1-B4EF-4862-8792-DC54BA47F895}" name="Transaction Amount (EUR)" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,12 +495,12 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="26.125" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="8" max="8" width="18.375" customWidth="1"/>
     <col min="9" max="10" width="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -438,7 +520,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="7" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -464,39 +546,39 @@
     </row>
     <row r="6" spans="1:10" ht="30">
       <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="E6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4">
         <v>1250</v>
       </c>
       <c r="E7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
         <v>7</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>8</v>
-      </c>
-      <c r="G7" t="s">
-        <v>9</v>
       </c>
       <c r="H7" s="4">
         <v>60</v>
@@ -504,19 +586,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <v>8200</v>
       </c>
       <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
       <c r="G8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H8" s="4">
         <v>0</v>
@@ -524,19 +606,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="4">
         <v>35000</v>
       </c>
       <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
         <v>13</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>15</v>
       </c>
       <c r="H9" s="4">
         <v>120</v>
@@ -544,19 +626,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="4">
         <v>5400</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H10" s="4">
         <v>250</v>
@@ -564,44 +646,49 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="4">
         <v>980</v>
       </c>
       <c r="E11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" t="s">
         <v>17</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>18</v>
-      </c>
-      <c r="G11" t="s">
-        <v>19</v>
       </c>
       <c r="H11" s="4">
         <v>45</v>
       </c>
     </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+    </row>
     <row r="14" spans="1:10" ht="30">
       <c r="A14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15" s="4">
         <v>1250</v>
@@ -621,7 +708,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16" s="4">
         <v>8200</v>
@@ -641,7 +728,7 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" s="4">
         <v>35000</v>
@@ -661,7 +748,7 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="4">
         <v>5400</v>
@@ -681,7 +768,7 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" s="4">
         <v>980</v>
@@ -701,7 +788,7 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -732,5 +819,9 @@
     <mergeCell ref="A21:J22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>